--- a/marketing_report/outputs/Cursos/Informe_Analitico/Tablas_Informe_Analitico.xlsx
+++ b/marketing_report/outputs/Cursos/Informe_Analitico/Tablas_Informe_Analitico.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>518</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>510</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>510</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -715,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>Facebook Lead Ads</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>213</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>209</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>209</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -767,17 +767,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Facebook Lead Ads</t>
+          <t>Origen (3)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>123</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -786,17 +786,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Origen (3)</t>
+          <t>Origen (4)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
@@ -805,17 +805,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chatbot</t>
+          <t>Desconocido</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
@@ -824,36 +824,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Origen (51)</t>
+          <t>Chatbot</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Origen (4)</t>
+          <t>Origen (130)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
@@ -862,17 +862,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Origen (103)</t>
+          <t>Origen (272)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
@@ -881,17 +881,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Origen (283)</t>
+          <t>Origen (41)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
@@ -900,209 +900,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Origen (285)</t>
+          <t>Origen (908)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Origen (272)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Origen (41)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Origen (130)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Origen (274)</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Origen (37)</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Origen (485)</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Origen (487)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Origen (491)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Origen (73)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Origen (908)</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
         <v>100</v>
       </c>
     </row>

--- a/marketing_report/outputs/Cursos/Informe_Analitico/Tablas_Informe_Analitico.xlsx
+++ b/marketing_report/outputs/Cursos/Informe_Analitico/Tablas_Informe_Analitico.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -748,17 +748,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Facebook Lead Ads</t>
+          <t>Origen (3)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -767,11 +767,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Origen (3)</t>
+          <t>Facebook Lead Ads</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
